--- a/tame_output/ON/bt/strategyON_20240804.xlsx
+++ b/tame_output/ON/bt/strategyON_20240804.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.7%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.9%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.3%</t>
+          <t>453.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-680.8%</t>
+          <t>-681.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-200.8%</t>
+          <t>-200.9%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.8%</t>
+          <t>-227.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.6%</t>
+          <t>-64.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2044"/>
+  <dimension ref="A1:G2045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.741353902931093</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48573,6 +48573,29 @@
       </c>
       <c r="G2044" t="n">
         <v>3.814158023649608</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" s="2" t="n">
+        <v>45507</v>
+      </c>
+      <c r="B2045" t="n">
+        <v>3.725123937759354</v>
+      </c>
+      <c r="C2045" t="n">
+        <v>3.833127068648268</v>
+      </c>
+      <c r="D2045" t="n">
+        <v>-5.198835280669472</v>
+      </c>
+      <c r="E2045" t="n">
+        <v>1.753236532066732</v>
+      </c>
+      <c r="F2045" t="n">
+        <v>-0.03510393804789813</v>
+      </c>
+      <c r="G2045" t="n">
+        <v>3.812064705819529</v>
       </c>
     </row>
   </sheetData>
